--- a/evaluation_multimodels/runs/2026-09-21-minimal32-five-self-included/pairs/claude_claude-opus-5_judge_medium__vs__qwen_qwen3.8-max_judge_medium.xlsx
+++ b/evaluation_multimodels/runs/2026-09-21-minimal32-five-self-included/pairs/claude_claude-opus-5_judge_medium__vs__qwen_qwen3.8-max_judge_medium.xlsx
@@ -2355,23 +2355,25 @@
       <c r="H2" t="b">
         <v>1</v>
       </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>0.002332963049411774</v>
+        <v>8097.036290972028</v>
       </c>
       <c r="M2" t="n">
-        <v>0.009290990419685841</v>
+        <v>1920.178750006016</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -2411,12 +2413,12 @@
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2455,23 +2457,25 @@
       <c r="H3" t="b">
         <v>1</v>
       </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>47155.80695797689</v>
+        <v>8068.261792010162</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02616696292534471</v>
+        <v>1774.023792007938</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -2511,12 +2515,12 @@
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2555,23 +2559,25 @@
       <c r="H4" t="b">
         <v>1</v>
       </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="n">
-        <v>12587.73716702126</v>
+        <v>9727.531708020251</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02687500091269612</v>
+        <v>1873.94012499135</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -2611,12 +2617,12 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2655,23 +2661,25 @@
       <c r="H5" t="b">
         <v>1</v>
       </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>34817.23541696556</v>
+        <v>10937.8850000212</v>
       </c>
       <c r="M5" t="n">
-        <v>0.03645796095952392</v>
+        <v>1878.011541964952</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -2711,12 +2719,12 @@
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2859,23 +2867,25 @@
       <c r="H7" t="b">
         <v>1</v>
       </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>0.002333021257072687</v>
+        <v>8572.911415947601</v>
       </c>
       <c r="M7" t="n">
-        <v>0.008250004611909389</v>
+        <v>1277.151459013112</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -2915,12 +2925,12 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -2959,23 +2969,25 @@
       <c r="H8" t="b">
         <v>1</v>
       </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>19507.41483300226</v>
+        <v>8654.533791996073</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01154100755229592</v>
+        <v>1677.295040979516</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -3015,12 +3027,12 @@
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -3059,23 +3071,25 @@
       <c r="H9" t="b">
         <v>1</v>
       </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>19151.53320797253</v>
+        <v>10618.75145800877</v>
       </c>
       <c r="M9" t="n">
-        <v>0.03791594645008445</v>
+        <v>1520.264333987143</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -3115,12 +3129,12 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -3159,6 +3173,7 @@
       <c r="H10" t="b">
         <v>1</v>
       </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>{"RL-01": [], "RL-02": [], "RL-03": [], "RL-04": [], "RL-05": [], "RL-06": []}</t>
@@ -3258,23 +3273,25 @@
       <c r="H11" t="b">
         <v>1</v>
       </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>14601.45362501498</v>
+        <v>12626.52704201173</v>
       </c>
       <c r="M11" t="n">
-        <v>0.04470802377909422</v>
+        <v>1809.505833953153</v>
       </c>
       <c r="Q11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -3314,12 +3331,12 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -3358,23 +3375,25 @@
       <c r="H12" t="b">
         <v>1</v>
       </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>112288.9520829776</v>
+        <v>7823.568124964368</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0196250039152801</v>
+        <v>1154.418874997646</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -3414,12 +3433,12 @@
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -3458,23 +3477,25 @@
       <c r="H13" t="b">
         <v>1</v>
       </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>13899.1027919692</v>
+        <v>10154.82379199238</v>
       </c>
       <c r="M13" t="n">
-        <v>0.02774997847154737</v>
+        <v>1938.173417001963</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -3514,12 +3535,12 @@
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -3558,23 +3579,25 @@
       <c r="H14" t="b">
         <v>1</v>
       </c>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>0.002458982635289431</v>
+        <v>6533.302083029412</v>
       </c>
       <c r="M14" t="n">
-        <v>0.00925001222640276</v>
+        <v>1121.700374991633</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -3614,12 +3637,12 @@
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -3658,23 +3681,25 @@
       <c r="H15" t="b">
         <v>1</v>
       </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>21752.19262501923</v>
+        <v>8356.600917002652</v>
       </c>
       <c r="M15" t="n">
-        <v>0.03095797728747129</v>
+        <v>1054.781750019174</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -3714,12 +3739,12 @@
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -3758,23 +3783,25 @@
       <c r="H16" t="b">
         <v>1</v>
       </c>
+      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>0.001957989297807217</v>
+        <v>2810.97754201619</v>
       </c>
       <c r="M16" t="n">
-        <v>0.007541966624557972</v>
+        <v>1916.060417017434</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -3814,12 +3841,12 @@
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -3858,23 +3885,25 @@
       <c r="H17" t="b">
         <v>1</v>
       </c>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>43334.74675001344</v>
+        <v>9103.984709014185</v>
       </c>
       <c r="M17" t="n">
-        <v>0.009792041964828968</v>
+        <v>1851.77854198264</v>
       </c>
       <c r="Q17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -3914,12 +3943,12 @@
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
@@ -3958,23 +3987,25 @@
       <c r="H18" t="b">
         <v>1</v>
       </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="n">
-        <v>10853.73987496132</v>
+        <v>8285.555082955398</v>
       </c>
       <c r="M18" t="n">
-        <v>0.02679199678823352</v>
+        <v>1244.56633295631</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["URLError", "URLError"]</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -4014,12 +4045,12 @@
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>NOT_ATTEMPTED</t>
+          <t>CONNECTION</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>RuntimeError: TRIAL_CIRCUIT_OPEN_NOT_ATTEMPTED: qwen Judge paused after observed repeated rate limits/timeouts or incomplete streams; prior successful judgements preserved; not a quality zero</t>
+          <t>ProviderCallError: qwen transport failed: URLError: &lt;urlopen error [Errno 8] nodename nor servname provided, or not known&gt;</t>
         </is>
       </c>
     </row>
